--- a/artfynd/A 40491-2023 artfynd.xlsx
+++ b/artfynd/A 40491-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>132352096</v>
       </c>
       <c r="B2" t="n">
-        <v>98171</v>
+        <v>98174</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 40491-2023 artfynd.xlsx
+++ b/artfynd/A 40491-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>132352096</v>
       </c>
       <c r="B2" t="n">
-        <v>98174</v>
+        <v>98182</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 40491-2023 artfynd.xlsx
+++ b/artfynd/A 40491-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>132352096</v>
       </c>
       <c r="B2" t="n">
-        <v>98182</v>
+        <v>98192</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 40491-2023 artfynd.xlsx
+++ b/artfynd/A 40491-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>132352096</v>
       </c>
       <c r="B2" t="n">
-        <v>98192</v>
+        <v>98193</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 40491-2023 artfynd.xlsx
+++ b/artfynd/A 40491-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>132352096</v>
       </c>
       <c r="B2" t="n">
-        <v>98193</v>
+        <v>98194</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 40491-2023 artfynd.xlsx
+++ b/artfynd/A 40491-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,45 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>132352096</v>
+        <v>132368100</v>
       </c>
       <c r="B2" t="n">
-        <v>98201</v>
+        <v>85590</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220686</v>
+        <v>1971</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kambräken</t>
+          <t>Stor sotdyna</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Blechnum spicant</t>
+          <t>Camarops polysperma</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Roth</t>
+          <t>(Mont.) J.H.Mill.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Toftasjön, Hl</t>
+          <t>Högåsen, Hl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>377525</v>
+        <v>377515</v>
       </c>
       <c r="R2" t="n">
-        <v>6285972</v>
+        <v>6285961</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -743,42 +746,338 @@
           <t>2026-04-11</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>14:01</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2026-04-11</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>14:01</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
+          <t>August Oljeqvist</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>August Oljeqvist, Jonas Göransson</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>128337194</v>
+      </c>
+      <c r="B3" t="n">
+        <v>96708</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>2180</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Blåmossa</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Leucobryum glaucum</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Toftasjön, Hl</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>377541</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6285942</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Halmstad</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Snöstorp</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>August Oljeqvist</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>August Oljeqvist, Gunnar Deltén Bönner, Veronica Palm, Julia Frejd, Philip Johansson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>132368103</v>
+      </c>
+      <c r="B4" t="n">
+        <v>75354</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>6427</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Glansfläck</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Diarthonis spadicea</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Leight.) Frisch &amp; al.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Högåsen, Hl</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>377515</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6285961</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Halmstad</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Snöstorp</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>August Oljeqvist</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>August Oljeqvist, Jonas Göransson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>132352096</v>
+      </c>
+      <c r="B5" t="n">
+        <v>98271</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>220686</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Kambräken</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Blechnum spicant</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(L.) Roth</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Toftasjön, Hl</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>377525</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6285972</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Halmstad</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Snöstorp</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>14:01</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>14:01</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
           <t>Jonas Göransson</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
+      <c r="AX5" t="inlineStr">
         <is>
           <t>Jonas Göransson, August Oljeqvist, Julia Frejd, Julia Lea Falk, Svea Nikula, Veronica Palm, Amanda Rudelius, Philip Johansson</t>
         </is>
       </c>
-      <c r="AY2" t="inlineStr"/>
+      <c r="AY5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 40491-2023 artfynd.xlsx
+++ b/artfynd/A 40491-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -773,6 +778,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132368100</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -870,6 +880,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128337194</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -971,6 +986,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132368103</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1078,8 +1098,19 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132352096</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>